--- a/artfynd/A 38550-2024 artfynd.xlsx
+++ b/artfynd/A 38550-2024 artfynd.xlsx
@@ -1353,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232853</v>
+        <v>121232855</v>
       </c>
       <c r="B8" t="n">
-        <v>78598</v>
+        <v>90693</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,21 +1369,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576766</v>
+        <v>576758</v>
       </c>
       <c r="R8" t="n">
-        <v>7187829</v>
+        <v>7187818</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232851</v>
+        <v>121232860</v>
       </c>
       <c r="B9" t="n">
-        <v>78598</v>
+        <v>90697</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576785</v>
+        <v>576779</v>
       </c>
       <c r="R9" t="n">
         <v>7187783</v>
@@ -1557,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232836</v>
+        <v>121232851</v>
       </c>
       <c r="B10" t="n">
-        <v>57348</v>
+        <v>78601</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1573,39 +1573,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576757</v>
+        <v>576785</v>
       </c>
       <c r="R10" t="n">
-        <v>7187761</v>
+        <v>7187783</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,10 +1659,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232849</v>
+        <v>121232841</v>
       </c>
       <c r="B11" t="n">
-        <v>90705</v>
+        <v>57351</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1680,34 +1675,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576767</v>
+        <v>576628</v>
       </c>
       <c r="R11" t="n">
-        <v>7187902</v>
+        <v>7187807</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1766,10 +1766,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121232838</v>
+        <v>121232857</v>
       </c>
       <c r="B12" t="n">
-        <v>57348</v>
+        <v>79711</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1778,43 +1778,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576756</v>
+        <v>576754</v>
       </c>
       <c r="R12" t="n">
-        <v>7187816</v>
+        <v>7187826</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,10 +1868,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121232860</v>
+        <v>121232849</v>
       </c>
       <c r="B13" t="n">
-        <v>90687</v>
+        <v>90715</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1889,21 +1884,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1913,10 +1908,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576779</v>
+        <v>576767</v>
       </c>
       <c r="R13" t="n">
-        <v>7187783</v>
+        <v>7187902</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1975,10 +1970,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121232845</v>
+        <v>121232836</v>
       </c>
       <c r="B14" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2020,10 +2015,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576609</v>
+        <v>576757</v>
       </c>
       <c r="R14" t="n">
-        <v>7187790</v>
+        <v>7187761</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2082,10 +2077,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121232841</v>
+        <v>121232838</v>
       </c>
       <c r="B15" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2127,10 +2122,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576628</v>
+        <v>576756</v>
       </c>
       <c r="R15" t="n">
-        <v>7187807</v>
+        <v>7187816</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2192,7 +2187,7 @@
         <v>121232847</v>
       </c>
       <c r="B16" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2296,10 +2291,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121232855</v>
+        <v>121232845</v>
       </c>
       <c r="B17" t="n">
-        <v>90683</v>
+        <v>57351</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2312,34 +2307,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576758</v>
+        <v>576609</v>
       </c>
       <c r="R17" t="n">
-        <v>7187818</v>
+        <v>7187790</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2398,10 +2398,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121232857</v>
+        <v>121232853</v>
       </c>
       <c r="B18" t="n">
-        <v>79708</v>
+        <v>78601</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2410,25 +2410,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2438,10 +2438,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576754</v>
+        <v>576766</v>
       </c>
       <c r="R18" t="n">
-        <v>7187826</v>
+        <v>7187829</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 38550-2024 artfynd.xlsx
+++ b/artfynd/A 38550-2024 artfynd.xlsx
@@ -1353,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232855</v>
+        <v>121232860</v>
       </c>
       <c r="B8" t="n">
-        <v>90693</v>
+        <v>90697</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,21 +1369,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576758</v>
+        <v>576779</v>
       </c>
       <c r="R8" t="n">
-        <v>7187818</v>
+        <v>7187783</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232860</v>
+        <v>121232841</v>
       </c>
       <c r="B9" t="n">
-        <v>90697</v>
+        <v>57351</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,34 +1471,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576779</v>
+        <v>576628</v>
       </c>
       <c r="R9" t="n">
-        <v>7187783</v>
+        <v>7187807</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,10 +1562,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232851</v>
+        <v>121232836</v>
       </c>
       <c r="B10" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1573,34 +1578,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576785</v>
+        <v>576757</v>
       </c>
       <c r="R10" t="n">
-        <v>7187783</v>
+        <v>7187761</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,7 +1669,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232841</v>
+        <v>121232838</v>
       </c>
       <c r="B11" t="n">
         <v>57351</v>
@@ -1704,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576628</v>
+        <v>576756</v>
       </c>
       <c r="R11" t="n">
-        <v>7187807</v>
+        <v>7187816</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1766,10 +1776,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121232857</v>
+        <v>121232849</v>
       </c>
       <c r="B12" t="n">
-        <v>79711</v>
+        <v>90715</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1778,25 +1788,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1806,10 +1816,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576754</v>
+        <v>576767</v>
       </c>
       <c r="R12" t="n">
-        <v>7187826</v>
+        <v>7187902</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,10 +1878,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121232849</v>
+        <v>121232851</v>
       </c>
       <c r="B13" t="n">
-        <v>90715</v>
+        <v>78601</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1884,21 +1894,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1908,10 +1918,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576767</v>
+        <v>576785</v>
       </c>
       <c r="R13" t="n">
-        <v>7187902</v>
+        <v>7187783</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1970,7 +1980,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121232836</v>
+        <v>121232845</v>
       </c>
       <c r="B14" t="n">
         <v>57351</v>
@@ -2015,10 +2025,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576757</v>
+        <v>576609</v>
       </c>
       <c r="R14" t="n">
-        <v>7187761</v>
+        <v>7187790</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,10 +2087,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121232838</v>
+        <v>121232853</v>
       </c>
       <c r="B15" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2093,39 +2103,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576756</v>
+        <v>576766</v>
       </c>
       <c r="R15" t="n">
-        <v>7187816</v>
+        <v>7187829</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2184,10 +2189,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121232847</v>
+        <v>121232857</v>
       </c>
       <c r="B16" t="n">
-        <v>57351</v>
+        <v>79711</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2196,43 +2201,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576597</v>
+        <v>576754</v>
       </c>
       <c r="R16" t="n">
-        <v>7187779</v>
+        <v>7187826</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2291,7 +2291,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121232845</v>
+        <v>121232847</v>
       </c>
       <c r="B17" t="n">
         <v>57351</v>
@@ -2336,10 +2336,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576609</v>
+        <v>576597</v>
       </c>
       <c r="R17" t="n">
-        <v>7187790</v>
+        <v>7187779</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2398,10 +2398,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121232853</v>
+        <v>121232855</v>
       </c>
       <c r="B18" t="n">
-        <v>78601</v>
+        <v>90693</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2414,21 +2414,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2438,10 +2438,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576766</v>
+        <v>576758</v>
       </c>
       <c r="R18" t="n">
-        <v>7187829</v>
+        <v>7187818</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 38550-2024 artfynd.xlsx
+++ b/artfynd/A 38550-2024 artfynd.xlsx
@@ -1356,7 +1356,7 @@
         <v>121232860</v>
       </c>
       <c r="B8" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232841</v>
+        <v>121232853</v>
       </c>
       <c r="B9" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,39 +1471,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576628</v>
+        <v>576766</v>
       </c>
       <c r="R9" t="n">
-        <v>7187807</v>
+        <v>7187829</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1557,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232836</v>
+        <v>121232845</v>
       </c>
       <c r="B10" t="n">
         <v>57351</v>
@@ -1607,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576757</v>
+        <v>576609</v>
       </c>
       <c r="R10" t="n">
-        <v>7187761</v>
+        <v>7187790</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232838</v>
+        <v>121232851</v>
       </c>
       <c r="B11" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1685,39 +1680,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576756</v>
+        <v>576785</v>
       </c>
       <c r="R11" t="n">
-        <v>7187816</v>
+        <v>7187783</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,10 +1766,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121232849</v>
+        <v>121232855</v>
       </c>
       <c r="B12" t="n">
-        <v>90715</v>
+        <v>90705</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1792,21 +1782,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1816,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576767</v>
+        <v>576758</v>
       </c>
       <c r="R12" t="n">
-        <v>7187902</v>
+        <v>7187818</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1878,10 +1868,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121232851</v>
+        <v>121232836</v>
       </c>
       <c r="B13" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1894,34 +1884,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576785</v>
+        <v>576757</v>
       </c>
       <c r="R13" t="n">
-        <v>7187783</v>
+        <v>7187761</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,7 +1975,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121232845</v>
+        <v>121232838</v>
       </c>
       <c r="B14" t="n">
         <v>57351</v>
@@ -2025,10 +2020,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576609</v>
+        <v>576756</v>
       </c>
       <c r="R14" t="n">
-        <v>7187790</v>
+        <v>7187816</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2087,10 +2082,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121232853</v>
+        <v>121232849</v>
       </c>
       <c r="B15" t="n">
-        <v>78601</v>
+        <v>90727</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2103,21 +2098,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2127,10 +2122,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576766</v>
+        <v>576767</v>
       </c>
       <c r="R15" t="n">
-        <v>7187829</v>
+        <v>7187902</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2192,7 +2187,7 @@
         <v>121232857</v>
       </c>
       <c r="B16" t="n">
-        <v>79711</v>
+        <v>79714</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2291,7 +2286,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121232847</v>
+        <v>121232841</v>
       </c>
       <c r="B17" t="n">
         <v>57351</v>
@@ -2336,10 +2331,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576597</v>
+        <v>576628</v>
       </c>
       <c r="R17" t="n">
-        <v>7187779</v>
+        <v>7187807</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2398,10 +2393,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121232855</v>
+        <v>121232847</v>
       </c>
       <c r="B18" t="n">
-        <v>90693</v>
+        <v>57351</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2414,34 +2409,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576758</v>
+        <v>576597</v>
       </c>
       <c r="R18" t="n">
-        <v>7187818</v>
+        <v>7187779</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 38550-2024 artfynd.xlsx
+++ b/artfynd/A 38550-2024 artfynd.xlsx
@@ -1353,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232860</v>
+        <v>121232841</v>
       </c>
       <c r="B8" t="n">
-        <v>90709</v>
+        <v>57351</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,34 +1369,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576779</v>
+        <v>576628</v>
       </c>
       <c r="R8" t="n">
-        <v>7187783</v>
+        <v>7187807</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,10 +1460,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232853</v>
+        <v>121232838</v>
       </c>
       <c r="B9" t="n">
-        <v>78604</v>
+        <v>57351</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,34 +1476,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576766</v>
+        <v>576756</v>
       </c>
       <c r="R9" t="n">
-        <v>7187829</v>
+        <v>7187816</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232845</v>
+        <v>121232857</v>
       </c>
       <c r="B10" t="n">
-        <v>57351</v>
+        <v>79714</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1569,43 +1579,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576609</v>
+        <v>576754</v>
       </c>
       <c r="R10" t="n">
-        <v>7187790</v>
+        <v>7187826</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1766,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121232855</v>
+        <v>121232860</v>
       </c>
       <c r="B12" t="n">
-        <v>90705</v>
+        <v>90710</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1782,21 +1787,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1806,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576758</v>
+        <v>576779</v>
       </c>
       <c r="R12" t="n">
-        <v>7187818</v>
+        <v>7187783</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1975,10 +1980,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121232838</v>
+        <v>121232853</v>
       </c>
       <c r="B14" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1991,39 +1996,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576756</v>
+        <v>576766</v>
       </c>
       <c r="R14" t="n">
-        <v>7187816</v>
+        <v>7187829</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2082,10 +2082,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121232849</v>
+        <v>121232847</v>
       </c>
       <c r="B15" t="n">
-        <v>90727</v>
+        <v>57351</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2098,34 +2098,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576767</v>
+        <v>576597</v>
       </c>
       <c r="R15" t="n">
-        <v>7187902</v>
+        <v>7187779</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2184,10 +2189,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121232857</v>
+        <v>121232845</v>
       </c>
       <c r="B16" t="n">
-        <v>79714</v>
+        <v>57351</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2196,38 +2201,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576754</v>
+        <v>576609</v>
       </c>
       <c r="R16" t="n">
-        <v>7187826</v>
+        <v>7187790</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2286,10 +2296,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121232841</v>
+        <v>121232855</v>
       </c>
       <c r="B17" t="n">
-        <v>57351</v>
+        <v>90706</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2302,39 +2312,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576628</v>
+        <v>576758</v>
       </c>
       <c r="R17" t="n">
-        <v>7187807</v>
+        <v>7187818</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2393,10 +2398,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121232847</v>
+        <v>121232849</v>
       </c>
       <c r="B18" t="n">
-        <v>57351</v>
+        <v>90728</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2409,39 +2414,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576597</v>
+        <v>576767</v>
       </c>
       <c r="R18" t="n">
-        <v>7187779</v>
+        <v>7187902</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 38550-2024 artfynd.xlsx
+++ b/artfynd/A 38550-2024 artfynd.xlsx
@@ -1353,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232841</v>
+        <v>121232853</v>
       </c>
       <c r="B8" t="n">
-        <v>57351</v>
+        <v>78607</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,39 +1369,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576628</v>
+        <v>576766</v>
       </c>
       <c r="R8" t="n">
-        <v>7187807</v>
+        <v>7187829</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232838</v>
+        <v>121232855</v>
       </c>
       <c r="B9" t="n">
-        <v>57351</v>
+        <v>90709</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,39 +1471,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576756</v>
+        <v>576758</v>
       </c>
       <c r="R9" t="n">
-        <v>7187816</v>
+        <v>7187818</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232857</v>
+        <v>121232845</v>
       </c>
       <c r="B10" t="n">
-        <v>79714</v>
+        <v>57354</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,38 +1569,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576754</v>
+        <v>576609</v>
       </c>
       <c r="R10" t="n">
-        <v>7187826</v>
+        <v>7187790</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232851</v>
+        <v>121232838</v>
       </c>
       <c r="B11" t="n">
-        <v>78604</v>
+        <v>57354</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1685,34 +1680,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576785</v>
+        <v>576756</v>
       </c>
       <c r="R11" t="n">
-        <v>7187783</v>
+        <v>7187816</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121232860</v>
+        <v>121232847</v>
       </c>
       <c r="B12" t="n">
-        <v>90710</v>
+        <v>57354</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1787,34 +1787,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576779</v>
+        <v>576597</v>
       </c>
       <c r="R12" t="n">
-        <v>7187783</v>
+        <v>7187779</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,10 +1878,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121232836</v>
+        <v>121232857</v>
       </c>
       <c r="B13" t="n">
-        <v>57351</v>
+        <v>79717</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1885,43 +1890,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576757</v>
+        <v>576754</v>
       </c>
       <c r="R13" t="n">
-        <v>7187761</v>
+        <v>7187826</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,10 +1980,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121232853</v>
+        <v>121232849</v>
       </c>
       <c r="B14" t="n">
-        <v>78604</v>
+        <v>90731</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1996,21 +1996,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576766</v>
+        <v>576767</v>
       </c>
       <c r="R14" t="n">
-        <v>7187829</v>
+        <v>7187902</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2082,10 +2082,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121232847</v>
+        <v>121232851</v>
       </c>
       <c r="B15" t="n">
-        <v>57351</v>
+        <v>78607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2098,39 +2098,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576597</v>
+        <v>576785</v>
       </c>
       <c r="R15" t="n">
-        <v>7187779</v>
+        <v>7187783</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2189,10 +2184,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121232845</v>
+        <v>121232836</v>
       </c>
       <c r="B16" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2234,10 +2229,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576609</v>
+        <v>576757</v>
       </c>
       <c r="R16" t="n">
-        <v>7187790</v>
+        <v>7187761</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2296,10 +2291,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121232855</v>
+        <v>121232841</v>
       </c>
       <c r="B17" t="n">
-        <v>90706</v>
+        <v>57354</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2312,34 +2307,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576758</v>
+        <v>576628</v>
       </c>
       <c r="R17" t="n">
-        <v>7187818</v>
+        <v>7187807</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2398,10 +2398,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121232849</v>
+        <v>121232860</v>
       </c>
       <c r="B18" t="n">
-        <v>90728</v>
+        <v>90713</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2414,21 +2414,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2438,10 +2438,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576767</v>
+        <v>576779</v>
       </c>
       <c r="R18" t="n">
-        <v>7187902</v>
+        <v>7187783</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 38550-2024 artfynd.xlsx
+++ b/artfynd/A 38550-2024 artfynd.xlsx
@@ -1353,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232853</v>
+        <v>121232847</v>
       </c>
       <c r="B8" t="n">
-        <v>78607</v>
+        <v>57354</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,34 +1369,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576766</v>
+        <v>576597</v>
       </c>
       <c r="R8" t="n">
-        <v>7187829</v>
+        <v>7187779</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1557,7 +1562,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232845</v>
+        <v>121232841</v>
       </c>
       <c r="B10" t="n">
         <v>57354</v>
@@ -1602,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576609</v>
+        <v>576628</v>
       </c>
       <c r="R10" t="n">
-        <v>7187790</v>
+        <v>7187807</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1771,10 +1776,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121232847</v>
+        <v>121232853</v>
       </c>
       <c r="B12" t="n">
-        <v>57354</v>
+        <v>78607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1787,39 +1792,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576597</v>
+        <v>576766</v>
       </c>
       <c r="R12" t="n">
-        <v>7187779</v>
+        <v>7187829</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121232857</v>
+        <v>121232860</v>
       </c>
       <c r="B13" t="n">
-        <v>79717</v>
+        <v>90713</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1890,25 +1890,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576754</v>
+        <v>576779</v>
       </c>
       <c r="R13" t="n">
-        <v>7187826</v>
+        <v>7187783</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2082,10 +2082,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121232851</v>
+        <v>121232857</v>
       </c>
       <c r="B15" t="n">
-        <v>78607</v>
+        <v>79717</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2094,25 +2094,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2122,10 +2122,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576785</v>
+        <v>576754</v>
       </c>
       <c r="R15" t="n">
-        <v>7187783</v>
+        <v>7187826</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121232841</v>
+        <v>121232851</v>
       </c>
       <c r="B17" t="n">
-        <v>57354</v>
+        <v>78607</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2307,39 +2307,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576628</v>
+        <v>576785</v>
       </c>
       <c r="R17" t="n">
-        <v>7187807</v>
+        <v>7187783</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2398,10 +2393,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121232860</v>
+        <v>121232845</v>
       </c>
       <c r="B18" t="n">
-        <v>90713</v>
+        <v>57354</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2414,34 +2409,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576779</v>
+        <v>576609</v>
       </c>
       <c r="R18" t="n">
-        <v>7187783</v>
+        <v>7187790</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 38550-2024 artfynd.xlsx
+++ b/artfynd/A 38550-2024 artfynd.xlsx
@@ -1353,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232847</v>
+        <v>121232853</v>
       </c>
       <c r="B8" t="n">
-        <v>57354</v>
+        <v>78608</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,39 +1369,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576597</v>
+        <v>576766</v>
       </c>
       <c r="R8" t="n">
-        <v>7187779</v>
+        <v>7187829</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232855</v>
+        <v>121232845</v>
       </c>
       <c r="B9" t="n">
-        <v>90709</v>
+        <v>57355</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,34 +1471,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576758</v>
+        <v>576609</v>
       </c>
       <c r="R9" t="n">
-        <v>7187818</v>
+        <v>7187790</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232841</v>
+        <v>121232857</v>
       </c>
       <c r="B10" t="n">
-        <v>57354</v>
+        <v>79718</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1574,43 +1574,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576628</v>
+        <v>576754</v>
       </c>
       <c r="R10" t="n">
-        <v>7187807</v>
+        <v>7187826</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232838</v>
+        <v>121232841</v>
       </c>
       <c r="B11" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576756</v>
+        <v>576628</v>
       </c>
       <c r="R11" t="n">
-        <v>7187816</v>
+        <v>7187807</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121232853</v>
+        <v>121232836</v>
       </c>
       <c r="B12" t="n">
-        <v>78607</v>
+        <v>57355</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1792,34 +1787,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576766</v>
+        <v>576757</v>
       </c>
       <c r="R12" t="n">
-        <v>7187829</v>
+        <v>7187761</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121232860</v>
+        <v>121232838</v>
       </c>
       <c r="B13" t="n">
-        <v>90713</v>
+        <v>57355</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1894,34 +1894,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576779</v>
+        <v>576756</v>
       </c>
       <c r="R13" t="n">
-        <v>7187783</v>
+        <v>7187816</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,10 +1985,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121232849</v>
+        <v>121232847</v>
       </c>
       <c r="B14" t="n">
-        <v>90731</v>
+        <v>57355</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1996,34 +2001,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576767</v>
+        <v>576597</v>
       </c>
       <c r="R14" t="n">
-        <v>7187902</v>
+        <v>7187779</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2082,10 +2092,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121232857</v>
+        <v>121232851</v>
       </c>
       <c r="B15" t="n">
-        <v>79717</v>
+        <v>78608</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2094,25 +2104,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2122,10 +2132,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576754</v>
+        <v>576785</v>
       </c>
       <c r="R15" t="n">
-        <v>7187826</v>
+        <v>7187783</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2184,10 +2194,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121232836</v>
+        <v>121232860</v>
       </c>
       <c r="B16" t="n">
-        <v>57354</v>
+        <v>90719</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2200,39 +2210,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576757</v>
+        <v>576779</v>
       </c>
       <c r="R16" t="n">
-        <v>7187761</v>
+        <v>7187783</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2291,10 +2296,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121232851</v>
+        <v>121232855</v>
       </c>
       <c r="B17" t="n">
-        <v>78607</v>
+        <v>90715</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2307,21 +2312,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2331,10 +2336,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576785</v>
+        <v>576758</v>
       </c>
       <c r="R17" t="n">
-        <v>7187783</v>
+        <v>7187818</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2393,10 +2398,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121232845</v>
+        <v>121232849</v>
       </c>
       <c r="B18" t="n">
-        <v>57354</v>
+        <v>90737</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2409,39 +2414,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576609</v>
+        <v>576767</v>
       </c>
       <c r="R18" t="n">
-        <v>7187790</v>
+        <v>7187902</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 38550-2024 artfynd.xlsx
+++ b/artfynd/A 38550-2024 artfynd.xlsx
@@ -1353,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232853</v>
+        <v>121232836</v>
       </c>
       <c r="B8" t="n">
-        <v>78608</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,34 +1369,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576766</v>
+        <v>576757</v>
       </c>
       <c r="R8" t="n">
-        <v>7187829</v>
+        <v>7187761</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,10 +1460,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232845</v>
+        <v>121232851</v>
       </c>
       <c r="B9" t="n">
-        <v>57355</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,39 +1476,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576609</v>
+        <v>576785</v>
       </c>
       <c r="R9" t="n">
-        <v>7187790</v>
+        <v>7187783</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232857</v>
+        <v>121232841</v>
       </c>
       <c r="B10" t="n">
-        <v>79718</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1574,38 +1574,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576754</v>
+        <v>576628</v>
       </c>
       <c r="R10" t="n">
-        <v>7187826</v>
+        <v>7187807</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,10 +1669,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232841</v>
+        <v>121232857</v>
       </c>
       <c r="B11" t="n">
-        <v>57355</v>
+        <v>79719</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1676,43 +1681,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576628</v>
+        <v>576754</v>
       </c>
       <c r="R11" t="n">
-        <v>7187807</v>
+        <v>7187826</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121232836</v>
+        <v>121232845</v>
       </c>
       <c r="B12" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576757</v>
+        <v>576609</v>
       </c>
       <c r="R12" t="n">
-        <v>7187761</v>
+        <v>7187790</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121232838</v>
+        <v>121232855</v>
       </c>
       <c r="B13" t="n">
-        <v>57355</v>
+        <v>90716</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1894,39 +1894,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576756</v>
+        <v>576758</v>
       </c>
       <c r="R13" t="n">
-        <v>7187816</v>
+        <v>7187818</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1985,10 +1980,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121232847</v>
+        <v>121232853</v>
       </c>
       <c r="B14" t="n">
-        <v>57355</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2001,39 +1996,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576597</v>
+        <v>576766</v>
       </c>
       <c r="R14" t="n">
-        <v>7187779</v>
+        <v>7187829</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2092,10 +2082,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121232851</v>
+        <v>121232860</v>
       </c>
       <c r="B15" t="n">
-        <v>78608</v>
+        <v>90720</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2108,21 +2098,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2132,7 +2122,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576785</v>
+        <v>576779</v>
       </c>
       <c r="R15" t="n">
         <v>7187783</v>
@@ -2194,10 +2184,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121232860</v>
+        <v>121232847</v>
       </c>
       <c r="B16" t="n">
-        <v>90719</v>
+        <v>57356</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2210,34 +2200,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576779</v>
+        <v>576597</v>
       </c>
       <c r="R16" t="n">
-        <v>7187783</v>
+        <v>7187779</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2296,10 +2291,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121232855</v>
+        <v>121232838</v>
       </c>
       <c r="B17" t="n">
-        <v>90715</v>
+        <v>57356</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2312,34 +2307,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576758</v>
+        <v>576756</v>
       </c>
       <c r="R17" t="n">
-        <v>7187818</v>
+        <v>7187816</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2401,7 +2401,7 @@
         <v>121232849</v>
       </c>
       <c r="B18" t="n">
-        <v>90737</v>
+        <v>90738</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 38550-2024 artfynd.xlsx
+++ b/artfynd/A 38550-2024 artfynd.xlsx
@@ -1353,7 +1353,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232836</v>
+        <v>121232838</v>
       </c>
       <c r="B8" t="n">
         <v>57356</v>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576757</v>
+        <v>576756</v>
       </c>
       <c r="R8" t="n">
-        <v>7187761</v>
+        <v>7187816</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1460,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232851</v>
+        <v>121232853</v>
       </c>
       <c r="B9" t="n">
         <v>78609</v>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576785</v>
+        <v>576766</v>
       </c>
       <c r="R9" t="n">
-        <v>7187783</v>
+        <v>7187829</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1562,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232841</v>
+        <v>121232845</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576628</v>
+        <v>576609</v>
       </c>
       <c r="R10" t="n">
-        <v>7187807</v>
+        <v>7187790</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,10 +1669,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232857</v>
+        <v>121232851</v>
       </c>
       <c r="B11" t="n">
-        <v>79719</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1681,25 +1681,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576754</v>
+        <v>576785</v>
       </c>
       <c r="R11" t="n">
-        <v>7187826</v>
+        <v>7187783</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121232845</v>
+        <v>121232857</v>
       </c>
       <c r="B12" t="n">
-        <v>57356</v>
+        <v>79719</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1783,43 +1783,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576609</v>
+        <v>576754</v>
       </c>
       <c r="R12" t="n">
-        <v>7187790</v>
+        <v>7187826</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1878,10 +1873,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121232855</v>
+        <v>121232849</v>
       </c>
       <c r="B13" t="n">
-        <v>90716</v>
+        <v>90738</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1894,21 +1889,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1918,10 +1913,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576758</v>
+        <v>576767</v>
       </c>
       <c r="R13" t="n">
-        <v>7187818</v>
+        <v>7187902</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,10 +1975,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121232853</v>
+        <v>121232847</v>
       </c>
       <c r="B14" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1996,34 +1991,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576766</v>
+        <v>576597</v>
       </c>
       <c r="R14" t="n">
-        <v>7187829</v>
+        <v>7187779</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2082,10 +2082,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121232860</v>
+        <v>121232836</v>
       </c>
       <c r="B15" t="n">
-        <v>90720</v>
+        <v>57356</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2098,34 +2098,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576779</v>
+        <v>576757</v>
       </c>
       <c r="R15" t="n">
-        <v>7187783</v>
+        <v>7187761</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2184,7 +2189,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121232847</v>
+        <v>121232841</v>
       </c>
       <c r="B16" t="n">
         <v>57356</v>
@@ -2229,10 +2234,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576597</v>
+        <v>576628</v>
       </c>
       <c r="R16" t="n">
-        <v>7187779</v>
+        <v>7187807</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2291,10 +2296,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121232838</v>
+        <v>121232860</v>
       </c>
       <c r="B17" t="n">
-        <v>57356</v>
+        <v>90720</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2307,39 +2312,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576756</v>
+        <v>576779</v>
       </c>
       <c r="R17" t="n">
-        <v>7187816</v>
+        <v>7187783</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2398,10 +2398,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121232849</v>
+        <v>121232855</v>
       </c>
       <c r="B18" t="n">
-        <v>90738</v>
+        <v>90716</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2414,21 +2414,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2438,10 +2438,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576767</v>
+        <v>576758</v>
       </c>
       <c r="R18" t="n">
-        <v>7187902</v>
+        <v>7187818</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 38550-2024 artfynd.xlsx
+++ b/artfynd/A 38550-2024 artfynd.xlsx
@@ -1353,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232838</v>
+        <v>121232849</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,39 +1369,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576756</v>
+        <v>576767</v>
       </c>
       <c r="R8" t="n">
-        <v>7187816</v>
+        <v>7187902</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232853</v>
+        <v>121232847</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,34 +1471,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576766</v>
+        <v>576597</v>
       </c>
       <c r="R9" t="n">
-        <v>7187829</v>
+        <v>7187779</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232845</v>
+        <v>121232860</v>
       </c>
       <c r="B10" t="n">
-        <v>57356</v>
+        <v>90720</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,39 +1578,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576609</v>
+        <v>576779</v>
       </c>
       <c r="R10" t="n">
-        <v>7187790</v>
+        <v>7187783</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1664,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232851</v>
+        <v>121232853</v>
       </c>
       <c r="B11" t="n">
         <v>78609</v>
@@ -1709,10 +1704,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576785</v>
+        <v>576766</v>
       </c>
       <c r="R11" t="n">
-        <v>7187783</v>
+        <v>7187829</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,10 +1766,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121232857</v>
+        <v>121232851</v>
       </c>
       <c r="B12" t="n">
-        <v>79719</v>
+        <v>78609</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1783,25 +1778,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1811,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576754</v>
+        <v>576785</v>
       </c>
       <c r="R12" t="n">
-        <v>7187826</v>
+        <v>7187783</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,10 +1868,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121232849</v>
+        <v>121232845</v>
       </c>
       <c r="B13" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1889,34 +1884,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576767</v>
+        <v>576609</v>
       </c>
       <c r="R13" t="n">
-        <v>7187902</v>
+        <v>7187790</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1975,10 +1975,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121232847</v>
+        <v>121232857</v>
       </c>
       <c r="B14" t="n">
-        <v>57356</v>
+        <v>79719</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1987,43 +1987,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576597</v>
+        <v>576754</v>
       </c>
       <c r="R14" t="n">
-        <v>7187779</v>
+        <v>7187826</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2082,7 +2077,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121232836</v>
+        <v>121232841</v>
       </c>
       <c r="B15" t="n">
         <v>57356</v>
@@ -2127,10 +2122,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576757</v>
+        <v>576628</v>
       </c>
       <c r="R15" t="n">
-        <v>7187761</v>
+        <v>7187807</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2189,7 +2184,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121232841</v>
+        <v>121232838</v>
       </c>
       <c r="B16" t="n">
         <v>57356</v>
@@ -2234,10 +2229,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576628</v>
+        <v>576756</v>
       </c>
       <c r="R16" t="n">
-        <v>7187807</v>
+        <v>7187816</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2296,10 +2291,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121232860</v>
+        <v>121232855</v>
       </c>
       <c r="B17" t="n">
-        <v>90720</v>
+        <v>90716</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2312,21 +2307,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2336,10 +2331,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576779</v>
+        <v>576758</v>
       </c>
       <c r="R17" t="n">
-        <v>7187783</v>
+        <v>7187818</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2398,10 +2393,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121232855</v>
+        <v>121232836</v>
       </c>
       <c r="B18" t="n">
-        <v>90716</v>
+        <v>57356</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2414,34 +2409,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576758</v>
+        <v>576757</v>
       </c>
       <c r="R18" t="n">
-        <v>7187818</v>
+        <v>7187761</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 38550-2024 artfynd.xlsx
+++ b/artfynd/A 38550-2024 artfynd.xlsx
@@ -1353,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121232849</v>
+        <v>121232841</v>
       </c>
       <c r="B8" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,34 +1369,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576767</v>
+        <v>576628</v>
       </c>
       <c r="R8" t="n">
-        <v>7187902</v>
+        <v>7187807</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,7 +1460,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121232847</v>
+        <v>121232838</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1500,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576597</v>
+        <v>576756</v>
       </c>
       <c r="R9" t="n">
-        <v>7187779</v>
+        <v>7187816</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232860</v>
+        <v>121232853</v>
       </c>
       <c r="B10" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,21 +1583,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1602,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576779</v>
+        <v>576766</v>
       </c>
       <c r="R10" t="n">
-        <v>7187783</v>
+        <v>7187829</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,10 +1669,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232853</v>
+        <v>121232855</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>90716</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1680,21 +1685,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1704,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576766</v>
+        <v>576758</v>
       </c>
       <c r="R11" t="n">
-        <v>7187829</v>
+        <v>7187818</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1766,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121232851</v>
+        <v>121232836</v>
       </c>
       <c r="B12" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1782,34 +1787,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576785</v>
+        <v>576757</v>
       </c>
       <c r="R12" t="n">
-        <v>7187783</v>
+        <v>7187761</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,10 +1878,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121232845</v>
+        <v>121232857</v>
       </c>
       <c r="B13" t="n">
-        <v>57356</v>
+        <v>79719</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1880,43 +1890,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576609</v>
+        <v>576754</v>
       </c>
       <c r="R13" t="n">
-        <v>7187790</v>
+        <v>7187826</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1975,10 +1980,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121232857</v>
+        <v>121232851</v>
       </c>
       <c r="B14" t="n">
-        <v>79719</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1987,25 +1992,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2015,10 +2020,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576754</v>
+        <v>576785</v>
       </c>
       <c r="R14" t="n">
-        <v>7187826</v>
+        <v>7187783</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2077,7 +2082,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121232841</v>
+        <v>121232845</v>
       </c>
       <c r="B15" t="n">
         <v>57356</v>
@@ -2122,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576628</v>
+        <v>576609</v>
       </c>
       <c r="R15" t="n">
-        <v>7187807</v>
+        <v>7187790</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2184,7 +2189,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121232838</v>
+        <v>121232847</v>
       </c>
       <c r="B16" t="n">
         <v>57356</v>
@@ -2229,10 +2234,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576756</v>
+        <v>576597</v>
       </c>
       <c r="R16" t="n">
-        <v>7187816</v>
+        <v>7187779</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2291,10 +2296,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121232855</v>
+        <v>121232860</v>
       </c>
       <c r="B17" t="n">
-        <v>90716</v>
+        <v>90720</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2307,21 +2312,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2331,10 +2336,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576758</v>
+        <v>576779</v>
       </c>
       <c r="R17" t="n">
-        <v>7187818</v>
+        <v>7187783</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2393,10 +2398,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121232836</v>
+        <v>121232849</v>
       </c>
       <c r="B18" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2409,39 +2414,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576757</v>
+        <v>576767</v>
       </c>
       <c r="R18" t="n">
-        <v>7187761</v>
+        <v>7187902</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 38550-2024 artfynd.xlsx
+++ b/artfynd/A 38550-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104001228</v>
+        <v>121232860</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
+        <v>90720</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -709,20 +709,19 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vilhelmina, Ås lm</t>
+          <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576779.9950461622</v>
+        <v>576779</v>
       </c>
       <c r="R2" t="n">
-        <v>7187783.230211183</v>
+        <v>7187783</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104001452</v>
+        <v>121232857</v>
       </c>
       <c r="B3" t="n">
-        <v>78596</v>
+        <v>79719</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,20 +811,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vilhelmina, Ås lm</t>
+          <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576754.5704439022</v>
+        <v>576754</v>
       </c>
       <c r="R3" t="n">
-        <v>7187826.067279709</v>
+        <v>7187826</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,22 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104001424</v>
+        <v>121232855</v>
       </c>
       <c r="B4" t="n">
-        <v>89388</v>
+        <v>90716</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,20 +913,19 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vilhelmina, Ås lm</t>
+          <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576758.5945400435</v>
+        <v>576758</v>
       </c>
       <c r="R4" t="n">
-        <v>7187818.922351746</v>
+        <v>7187818</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,22 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104001649</v>
+        <v>121232853</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,20 +1015,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vilhelmina, Ås lm</t>
+          <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576766.438400572</v>
+        <v>576766</v>
       </c>
       <c r="R5" t="n">
-        <v>7187829.354614776</v>
+        <v>7187829</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,22 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104001251</v>
+        <v>121232851</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,20 +1117,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vilhelmina, Ås lm</t>
+          <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576785.1140227034</v>
+        <v>576785</v>
       </c>
       <c r="R6" t="n">
-        <v>7187783.36094195</v>
+        <v>7187783</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,22 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,22 +1173,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104001666</v>
+        <v>121232849</v>
       </c>
       <c r="B7" t="n">
-        <v>89410</v>
+        <v>90738</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,20 +1219,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vilhelmina, Ås lm</t>
+          <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576767.5641125741</v>
+        <v>576767</v>
       </c>
       <c r="R7" t="n">
-        <v>7187902.285300456</v>
+        <v>7187902</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1311,22 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,12 +1275,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna-Sara Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1567,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121232853</v>
+        <v>121232836</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,34 +1517,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576766</v>
+        <v>576757</v>
       </c>
       <c r="R10" t="n">
-        <v>7187829</v>
+        <v>7187761</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121232855</v>
+        <v>121232845</v>
       </c>
       <c r="B11" t="n">
-        <v>90716</v>
+        <v>57356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1685,34 +1624,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576758</v>
+        <v>576609</v>
       </c>
       <c r="R11" t="n">
-        <v>7187818</v>
+        <v>7187790</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,7 +1715,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121232836</v>
+        <v>121232847</v>
       </c>
       <c r="B12" t="n">
         <v>57356</v>
@@ -1816,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576757</v>
+        <v>576597</v>
       </c>
       <c r="R12" t="n">
-        <v>7187761</v>
+        <v>7187779</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1875,628 +1819,6 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>121232857</v>
-      </c>
-      <c r="B13" t="n">
-        <v>79719</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Björnberget, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>576754</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7187826</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>121232851</v>
-      </c>
-      <c r="B14" t="n">
-        <v>78609</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Björnberget, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>576785</v>
-      </c>
-      <c r="R14" t="n">
-        <v>7187783</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>121232845</v>
-      </c>
-      <c r="B15" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Björnberget, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>576609</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7187790</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>121232847</v>
-      </c>
-      <c r="B16" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Björnberget, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>576597</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7187779</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>121232860</v>
-      </c>
-      <c r="B17" t="n">
-        <v>90720</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Björnberget, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>576779</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7187783</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>121232849</v>
-      </c>
-      <c r="B18" t="n">
-        <v>90738</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Björnberget, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>576767</v>
-      </c>
-      <c r="R18" t="n">
-        <v>7187902</v>
-      </c>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
